--- a/content/post/drafts/season-prediction/ladies_breakthrough_predictor-selection-results.xlsx
+++ b/content/post/drafts/season-prediction/ladies_breakthrough_predictor-selection-results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
@@ -32,73 +32,73 @@
     <t xml:space="preserve">Age</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04407098109891</t>
+    <t xml:space="preserve">2.05317073128709</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35896113735502</t>
+    <t xml:space="preserve">1.39339005504337</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Distance_F</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454119037991849</t>
+    <t xml:space="preserve">0.450644005009632</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Pelo</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087405947434346</t>
+    <t xml:space="preserve">0.0157326570262797</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Distance</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0196280201762633</t>
+    <t xml:space="preserve">-0.00320838424163072</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_C</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.292910945778965</t>
+    <t xml:space="preserve">-0.348461658271353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Sprint_C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.411399390207534</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Distance_C</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.327860232315771</t>
+    <t xml:space="preserve">-0.422622663189588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.551390428150187</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Sprint_F</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.510171759328955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.587106555350285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.635094692054671</t>
+    <t xml:space="preserve">-0.664216930155811</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_F</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.659362982485548</t>
+    <t xml:space="preserve">-0.692675483471835</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Sprint</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.951677956742188</t>
+    <t xml:space="preserve">-0.81896251067843</t>
   </si>
   <si>
     <t xml:space="preserve">Model</t>
@@ -194,28 +194,25 @@
     <t xml:space="preserve">                         Estimate Std. Error z value Pr(&gt;|z|)    </t>
   </si>
   <si>
-    <t xml:space="preserve">(Intercept)            -11.090696   2.018738  -5.494 3.93e-08 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age                     -0.114376   0.036082  -3.170  0.00152 ** </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points  -1.268847   1.032827  -1.229  0.21925    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance_F         -0.008061   0.002785  -2.894  0.00380 ** </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Pelo                0.007364   0.002300   3.201  0.00137 ** </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Distance            0.007495   0.003178   2.358  0.01835 *  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual deviance: 585.90  on 4100  degrees of freedom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIC: 597.9</t>
+    <t xml:space="preserve">(Intercept)            -12.941936   1.901595  -6.806 1.00e-11 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age                     -0.116526   0.036380  -3.203  0.00136 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points  -0.941219   1.033606  -0.911  0.36250    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Distance_F         -0.002621   0.001700  -1.542  0.12306    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_Pelo                0.010875   0.001633   6.660 2.74e-11 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual deviance: 591.71  on 4101  degrees of freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIC: 601.71</t>
   </si>
 </sst>
 </file>
@@ -580,7 +577,7 @@
         <v>60.3367916036485</v>
       </c>
       <c r="C3" t="n">
-        <v>93.609529583726</v>
+        <v>95.2336116899696</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -594,7 +591,7 @@
         <v>81.5415771171013</v>
       </c>
       <c r="C4" t="n">
-        <v>12.9602331069424</v>
+        <v>11.1768438117904</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -608,7 +605,7 @@
         <v>28.6437408869631</v>
       </c>
       <c r="C5" t="n">
-        <v>40.6135427485627</v>
+        <v>34.5705005440528</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -622,7 +619,7 @@
         <v>57.4802538794331</v>
       </c>
       <c r="C6" t="n">
-        <v>7.83518141059453</v>
+        <v>4.70194075283765</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -636,7 +633,7 @@
         <v>14.2795661590737</v>
       </c>
       <c r="C7" t="n">
-        <v>29.5559869787924</v>
+        <v>24.4710004785492</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -647,10 +644,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>7.36356349202183</v>
+        <v>17.9476216056288</v>
       </c>
       <c r="C8" t="n">
-        <v>34.0309327473086</v>
+        <v>16.6252392699139</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -661,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>17.6693129218879</v>
+        <v>7.36356349202183</v>
       </c>
       <c r="C9" t="n">
-        <v>11.8611663539169</v>
+        <v>26.3730443278751</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -675,10 +672,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>17.9476216056288</v>
+        <v>0.765180578761842</v>
       </c>
       <c r="C10" t="n">
-        <v>6.49996257500085</v>
+        <v>24.3094920623206</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -689,10 +686,10 @@
         <v>22</v>
       </c>
       <c r="B11" t="n">
-        <v>0.765180578761842</v>
+        <v>17.6693129218879</v>
       </c>
       <c r="C11" t="n">
-        <v>20.1865260313074</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -706,7 +703,7 @@
         <v>6.8300690372843</v>
       </c>
       <c r="C12" t="n">
-        <v>12.6303585118169</v>
+        <v>8.84871019465421</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -720,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>7.18080401353026</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -753,7 +750,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>0.860602318628461</v>
+        <v>0.876416611063451</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
@@ -764,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.88921275071413</v>
+        <v>0.883877814368281</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -999,37 +996,37 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -1039,21 +1036,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
         <v>33</v>
       </c>
     </row>
